--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>G.M.V. COLLEGE / LUCERITOS DEL SABER / PINCELADAS DE COLORES</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.78453</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.86287</v>
-      </c>
-      <c r="I2" t="n">
-        <v>204</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.78453</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.86287</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>TRILCE CHICLAYO</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.78336</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.84587999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>283</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.78336</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.84588</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>11004 SAN PEDRO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.760561</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.85551100000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>469</v>
-      </c>
-      <c r="J4" t="n">
-        <v>19</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.760561</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.855511</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>003 LOS PASTORCITOS DE LA VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.7642</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.8279</v>
-      </c>
-      <c r="I5" t="n">
-        <v>386</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.7642</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.8279</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>004 ANGELITOS DE MARIA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.7787</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.83459999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>322</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.7787</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.8346</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>10021 SAN JOSE</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.774947</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.84786800000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4772</v>
-      </c>
-      <c r="J7" t="n">
-        <v>216</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.774947</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.847868</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4772</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>022 COSOMITO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.76708</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.84975</v>
-      </c>
-      <c r="I8" t="n">
-        <v>431</v>
-      </c>
-      <c r="J8" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.76708</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.84975</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>031 ANGELITOS DEL CIELO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.7705</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.871</v>
-      </c>
-      <c r="I9" t="n">
-        <v>258</v>
-      </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.7705</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.871</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>048 SEMILLLITAS DE JESUS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.76523</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.84604</v>
-      </c>
-      <c r="I10" t="n">
-        <v>238</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.76523</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.84604</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>049 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.78322</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.83533</v>
-      </c>
-      <c r="I11" t="n">
-        <v>512</v>
-      </c>
-      <c r="J11" t="n">
-        <v>20</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.78322</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.83533</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>002 MARAVILLAS DE JESUS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.7841</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.84052</v>
-      </c>
-      <c r="I12" t="n">
-        <v>479</v>
-      </c>
-      <c r="J12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.7841</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.84052</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>119 FELIPE ALVA Y ALVA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-6.75915</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.85954</v>
-      </c>
-      <c r="I13" t="n">
-        <v>218</v>
-      </c>
-      <c r="J13" t="n">
-        <v>9</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-6.75915</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.85954</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>121 NUESTRA SEÑORA DEL PILAR</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-6.77958</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.86658</v>
-      </c>
-      <c r="I14" t="n">
-        <v>250</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-6.77958</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.86658</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>11223 FELIX TELLO ROJAS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-6.76423</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.85514999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>787</v>
-      </c>
-      <c r="J15" t="n">
-        <v>39</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-6.76423</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.85515</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>10002</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-6.778622</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.867817</v>
-      </c>
-      <c r="I16" t="n">
-        <v>669</v>
-      </c>
-      <c r="J16" t="n">
-        <v>29</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-6.778622</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.867817</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>10003</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-6.76731</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.83222000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>814</v>
-      </c>
-      <c r="J17" t="n">
-        <v>30</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-6.76731</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.83222</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>10024 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-6.777221</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-79.84842999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>760</v>
-      </c>
-      <c r="J18" t="n">
-        <v>38</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-6.777221</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.84843</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>10026 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-6.77844</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-79.84301000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>357</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-6.77844</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.84301</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>10040 SANTIAGO CASSINELLI CHIAPPE</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-6.76347</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-79.84465</v>
-      </c>
-      <c r="I20" t="n">
-        <v>499</v>
-      </c>
-      <c r="J20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-6.76347</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-79.84465</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>10042 MONSEÑOR JUAN TOMIS STACK</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-6.76565</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-79.85681200000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1528</v>
-      </c>
-      <c r="J21" t="n">
-        <v>77</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-6.76565</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-79.856812</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>10223 RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-6.76661</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-79.85937</v>
-      </c>
-      <c r="I22" t="n">
-        <v>418</v>
-      </c>
-      <c r="J22" t="n">
-        <v>17</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-6.76661</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-79.85937</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>11001 LEONCIO PRADO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-6.76989</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-79.83103</v>
-      </c>
-      <c r="I23" t="n">
-        <v>586</v>
-      </c>
-      <c r="J23" t="n">
-        <v>29</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-6.76989</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-79.83103</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>11006 RAMON ESPINOZA SIERRA / RAMON ESPINOZA SIERRA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-6.76582</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-79.84587000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>758</v>
-      </c>
-      <c r="J24" t="n">
-        <v>33</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-6.76582</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-79.84587</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>11014 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-6.78359</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-79.83574</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1729</v>
-      </c>
-      <c r="J25" t="n">
-        <v>80</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-6.78359</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-79.83574</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>11015 COMANDANTE ELIAS AGUIRRE</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-6.77085</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-79.83813000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>805</v>
-      </c>
-      <c r="J26" t="n">
-        <v>31</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-6.77085</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-79.83813</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>11016 JUAN MEJIA BACA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-6.77697</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-79.8476</v>
-      </c>
-      <c r="I27" t="n">
-        <v>420</v>
-      </c>
-      <c r="J27" t="n">
-        <v>28</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-6.77697</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-79.8476</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>11017 NICOLAS LA TORRE GARCIA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-6.77065</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-79.84687</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1059</v>
-      </c>
-      <c r="J28" t="n">
-        <v>46</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-6.77065</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-79.84687</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>11023 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-6.77101</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-79.85279</v>
-      </c>
-      <c r="I29" t="n">
-        <v>790</v>
-      </c>
-      <c r="J29" t="n">
-        <v>35</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-6.77101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-79.85279</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>11024 JOSE QUIÑONES GONZALES</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-6.77157</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-79.86826000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>744</v>
-      </c>
-      <c r="J30" t="n">
-        <v>32</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-6.77157</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-79.86826</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>10828</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-6.77219</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-79.84822</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1310</v>
-      </c>
-      <c r="J31" t="n">
-        <v>44</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-6.77219</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-79.84822</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>10824</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-6.77918</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-79.84684</v>
-      </c>
-      <c r="I32" t="n">
-        <v>325</v>
-      </c>
-      <c r="J32" t="n">
-        <v>19</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-6.77918</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-79.84684</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>11003 KARL WEISS</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-6.77517</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-79.83092000000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>3060</v>
-      </c>
-      <c r="J33" t="n">
-        <v>128</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-6.77517</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-79.83092</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>10030</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-6.773036</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-79.86439799999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>875</v>
-      </c>
-      <c r="J34" t="n">
-        <v>39</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-6.773036</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-79.864398</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-6.76905</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-79.87049</v>
-      </c>
-      <c r="I35" t="n">
-        <v>995</v>
-      </c>
-      <c r="J35" t="n">
-        <v>45</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-6.76905</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-79.87049</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>10925 CESAR VALLEJO / CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-6.76145</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-79.8254</v>
-      </c>
-      <c r="I36" t="n">
-        <v>687</v>
-      </c>
-      <c r="J36" t="n">
-        <v>42</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-6.76145</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-79.8254</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>11051 MARIA REICHE</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-6.76593</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-79.8259</v>
-      </c>
-      <c r="I37" t="n">
-        <v>595</v>
-      </c>
-      <c r="J37" t="n">
-        <v>22</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-6.76593</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-79.8259</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>10156</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-6.76624</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-79.82217</v>
-      </c>
-      <c r="I38" t="n">
-        <v>211</v>
-      </c>
-      <c r="J38" t="n">
-        <v>8</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-6.76624</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-79.82217</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>11124 NUESTRA SEÑORA DE LA PAZ</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-6.78063</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-79.8647</v>
-      </c>
-      <c r="I39" t="n">
-        <v>762</v>
-      </c>
-      <c r="J39" t="n">
-        <v>47</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-6.78063</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-79.8647</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>11151 MONSEÑOR AUGUSTO VARGAS ALZAMORA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-6.76049</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-79.85934</v>
-      </c>
-      <c r="I40" t="n">
-        <v>620</v>
-      </c>
-      <c r="J40" t="n">
-        <v>27</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-6.76049</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-79.85934</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>ROSA FLORES DE OLIVA</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-6.76938</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-79.86447</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1652</v>
-      </c>
-      <c r="J41" t="n">
-        <v>75</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-6.76938</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-79.86447</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1652</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>PEDRO ABEL LABARTHE DURAND</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-6.77495</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-79.84011</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1440</v>
-      </c>
-      <c r="J42" t="n">
-        <v>96</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-6.77495</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-79.84011</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-6.7819</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-79.8361</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1453</v>
-      </c>
-      <c r="J43" t="n">
-        <v>69</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-6.7819</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-79.8361</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>SANTA MAGDALENA SOFIA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-6.77077</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-79.84768</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2089</v>
-      </c>
-      <c r="J44" t="n">
-        <v>72</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-6.77077</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-79.84768</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-6.7592</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-79.85850000000001</v>
-      </c>
-      <c r="I45" t="n">
-        <v>700</v>
-      </c>
-      <c r="J45" t="n">
-        <v>38</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-6.7592</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-79.8585</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>10825 JUAN XXIII</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-6.7741</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-79.8694</v>
-      </c>
-      <c r="I46" t="n">
-        <v>640</v>
-      </c>
-      <c r="J46" t="n">
-        <v>25</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-6.7741</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-79.8694</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>015 SANTA MARIA DE LOS NIÑOS</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-6.77141</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-79.86599</v>
-      </c>
-      <c r="I47" t="n">
-        <v>259</v>
-      </c>
-      <c r="J47" t="n">
-        <v>11</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-6.77141</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-79.86599</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>MANUEL PARDO</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-6.765613</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-79.842326</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1714</v>
-      </c>
-      <c r="J48" t="n">
-        <v>78</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-6.765613</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-79.842326</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>BEATA IMELDA</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-6.76905</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-79.83877</v>
-      </c>
-      <c r="I49" t="n">
-        <v>450</v>
-      </c>
-      <c r="J49" t="n">
-        <v>56</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-6.76905</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-79.83877</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>SANTA ANGELA</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-6.78799</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-79.84678</v>
-      </c>
-      <c r="I50" t="n">
-        <v>736</v>
-      </c>
-      <c r="J50" t="n">
-        <v>50</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-6.78799</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-79.84678</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>SANTA MARIA REINA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-6.78525</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-79.84645999999999</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1502</v>
-      </c>
-      <c r="J51" t="n">
-        <v>83</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-6.78525</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-79.84646</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>CHICLAYO</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-6.7688</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-79.84683</v>
-      </c>
-      <c r="I52" t="n">
-        <v>42</v>
-      </c>
-      <c r="J52" t="n">
-        <v>5</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-6.7688</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-79.84683</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>CAPITAN FAP RENAN ELIAS OLIVERA</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-6.77548</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-79.82107000000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>328</v>
-      </c>
-      <c r="J53" t="n">
-        <v>44</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-6.77548</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-79.82107</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>FE Y ALEGRIA 28</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-6.77826</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-79.86399</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1374</v>
-      </c>
-      <c r="J54" t="n">
-        <v>69</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-6.77826</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-79.86399</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>ROSA MARIA CHECA</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-6.77057</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-79.86144</v>
-      </c>
-      <c r="I55" t="n">
-        <v>384</v>
-      </c>
-      <c r="J55" t="n">
-        <v>29</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-6.77057</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-79.86144</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>EL NAZARENO</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-6.76912</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-79.84189000000001</v>
-      </c>
-      <c r="I56" t="n">
-        <v>349</v>
-      </c>
-      <c r="J56" t="n">
-        <v>26</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-6.76912</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-79.84189</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>SANTA LUCIA SCHOOL</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-6.77243</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-79.86939</v>
-      </c>
-      <c r="I57" t="n">
-        <v>162</v>
-      </c>
-      <c r="J57" t="n">
-        <v>21</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-6.77243</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-79.86939</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>LA INMACULADA</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-6.77318</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-79.83649</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1497</v>
-      </c>
-      <c r="J58" t="n">
-        <v>47</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-6.77318</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-79.83649</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>ADVENTISTA CHICLAYO</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-6.76707</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-79.84105</v>
-      </c>
-      <c r="I59" t="n">
-        <v>211</v>
-      </c>
-      <c r="J59" t="n">
-        <v>18</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-6.76707</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-79.84105</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>SAN GABRIEL</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-6.76578</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-79.84161</v>
-      </c>
-      <c r="I60" t="n">
-        <v>312</v>
-      </c>
-      <c r="J60" t="n">
-        <v>22</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-6.76578</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-79.84161</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-6.77435</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-79.83708</v>
-      </c>
-      <c r="I61" t="n">
-        <v>274</v>
-      </c>
-      <c r="J61" t="n">
-        <v>22</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-6.77435</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-79.83708</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>JORGE BASADRE</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-6.77088</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-79.83678</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1399</v>
-      </c>
-      <c r="J62" t="n">
-        <v>65</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-6.77088</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-79.83678</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>APPUL COLLEGE</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-6.77401</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-79.84325</v>
-      </c>
-      <c r="I63" t="n">
-        <v>762</v>
-      </c>
-      <c r="J63" t="n">
-        <v>42</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-6.77401</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-79.84325</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>FLEMING COLLEGE</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-6.76605</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-79.82637</v>
-      </c>
-      <c r="I64" t="n">
-        <v>865</v>
-      </c>
-      <c r="J64" t="n">
-        <v>41</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-6.76605</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-79.82637</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>11027 DIVINO NIÑO DEL MILAGRO</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-6.90712</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-79.86002999999999</v>
-      </c>
-      <c r="I65" t="n">
-        <v>957</v>
-      </c>
-      <c r="J65" t="n">
-        <v>36</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-6.90712</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-79.86003</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-6.9075</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-79.85924</v>
-      </c>
-      <c r="I66" t="n">
-        <v>813</v>
-      </c>
-      <c r="J66" t="n">
-        <v>40</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-6.9075</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-79.85924</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>024 LA INMACULADA</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-6.75102</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-79.83651999999999</v>
-      </c>
-      <c r="I67" t="n">
-        <v>209</v>
-      </c>
-      <c r="J67" t="n">
-        <v>9</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-6.75102</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-79.83652</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>MANUEL ANTONIO RIVAS</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-6.75605</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-79.84058</v>
-      </c>
-      <c r="I68" t="n">
-        <v>306</v>
-      </c>
-      <c r="J68" t="n">
-        <v>22</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-6.75605</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-79.84058</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>10982</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-6.816828</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-79.85383</v>
-      </c>
-      <c r="I69" t="n">
-        <v>335</v>
-      </c>
-      <c r="J69" t="n">
-        <v>17</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-6.816828</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-79.85383</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>10054</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-6.82902</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-79.87584</v>
-      </c>
-      <c r="I70" t="n">
-        <v>436</v>
-      </c>
-      <c r="J70" t="n">
-        <v>24</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-6.82902</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-79.87584</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>PERUANO CANADIENSE</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-6.772027</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-79.832035</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1824</v>
-      </c>
-      <c r="J71" t="n">
-        <v>59</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-6.772027</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-79.832035</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>ALGARROBOS</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-6.800517</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-79.880573</v>
-      </c>
-      <c r="I72" t="n">
-        <v>620</v>
-      </c>
-      <c r="J72" t="n">
-        <v>52</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-6.800517</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-79.880573</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>10020</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-6.9216</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-79.58629999999999</v>
-      </c>
-      <c r="I73" t="n">
-        <v>442</v>
-      </c>
-      <c r="J73" t="n">
-        <v>18</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-6.9216</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-79.5863</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>JOSE DOMINGO ATOCHE</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-6.7362</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-79.6407</v>
-      </c>
-      <c r="I74" t="n">
-        <v>587</v>
-      </c>
-      <c r="J74" t="n">
-        <v>38</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-6.7362</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-79.6407</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>GREGORIO ODAR MORE</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-6.7445</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-79.54170000000001</v>
-      </c>
-      <c r="I75" t="n">
-        <v>282</v>
-      </c>
-      <c r="J75" t="n">
-        <v>24</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-6.7445</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-79.5417</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>11512</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-6.7441</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-79.5416</v>
-      </c>
-      <c r="I76" t="n">
-        <v>306</v>
-      </c>
-      <c r="J76" t="n">
-        <v>15</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-6.7441</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-79.5416</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>11501</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-6.770031</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-79.77616</v>
-      </c>
-      <c r="I77" t="n">
-        <v>683</v>
-      </c>
-      <c r="J77" t="n">
-        <v>34</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-6.770031</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-79.77616</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>11589 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-6.6918</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-79.7037</v>
-      </c>
-      <c r="I78" t="n">
-        <v>264</v>
-      </c>
-      <c r="J78" t="n">
-        <v>16</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-6.6918</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-79.7037</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>COAR LAMBAYEQUE</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-6.776861</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-79.847033</v>
-      </c>
-      <c r="I79" t="n">
-        <v>292</v>
-      </c>
-      <c r="J79" t="n">
-        <v>32</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-6.776861</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-79.847033</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>JUAN MEJIA BACA</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-6.77562</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-79.83226000000001</v>
-      </c>
-      <c r="I80" t="n">
-        <v>705</v>
-      </c>
-      <c r="J80" t="n">
-        <v>14</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-6.77562</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-79.83226</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>UNIVERSIA</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-6.76965</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-79.83353</v>
-      </c>
-      <c r="I81" t="n">
-        <v>206</v>
-      </c>
-      <c r="J81" t="n">
-        <v>18</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-6.76965</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-79.83353</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-6.78558</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-79.86507</v>
-      </c>
-      <c r="I82" t="n">
-        <v>397</v>
-      </c>
-      <c r="J82" t="n">
-        <v>28</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-6.78558</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-79.86507</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>DEPORTIVO ADEU</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-6.77239</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-79.840628</v>
-      </c>
-      <c r="I83" t="n">
-        <v>287</v>
-      </c>
-      <c r="J83" t="n">
-        <v>25</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-6.77239</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-79.840628</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>030 VICTORIA SILVA DE DALL'ORSO</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-6.77464</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-79.84671</v>
-      </c>
-      <c r="I84" t="n">
-        <v>467</v>
-      </c>
-      <c r="J84" t="n">
-        <v>19</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-6.77464</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-79.84671</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>PAUL HARRIS COLLEGE</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-6.77066</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-79.84223</v>
-      </c>
-      <c r="I85" t="n">
-        <v>285</v>
-      </c>
-      <c r="J85" t="n">
-        <v>17</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-6.77066</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-79.84223</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>MARIO VARGAS LLOSA</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-6.77441</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-79.83539</v>
-      </c>
-      <c r="I86" t="n">
-        <v>200</v>
-      </c>
-      <c r="J86" t="n">
-        <v>21</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-6.77441</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-79.83539</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>CRECIENDO CON AMOR</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-6.78444</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-79.84452</v>
-      </c>
-      <c r="I87" t="n">
-        <v>314</v>
-      </c>
-      <c r="J87" t="n">
-        <v>21</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-6.78444</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-79.84452</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>AMIGOS SCHOOL</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-6.76637</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-79.83687999999999</v>
-      </c>
-      <c r="I88" t="n">
-        <v>290</v>
-      </c>
-      <c r="J88" t="n">
-        <v>23</v>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-6.76637</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-79.83688</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>FREDERICK SANGER</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-6.789298</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-79.850353</v>
-      </c>
-      <c r="I89" t="n">
-        <v>224</v>
-      </c>
-      <c r="J89" t="n">
-        <v>17</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-6.789298</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-79.850353</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>MATER ADMIRABILIS</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-6.750883</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-79.840113</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1308</v>
-      </c>
-      <c r="J90" t="n">
-        <v>72</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-6.750883</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-79.840113</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>UN NUEVO TUMAN</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-6.750425</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-79.703452</v>
-      </c>
-      <c r="I91" t="n">
-        <v>335</v>
-      </c>
-      <c r="J91" t="n">
-        <v>25</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-6.750425</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-79.703452</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>JOYITAS DE JESUS</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-6.718336</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-79.770183</v>
-      </c>
-      <c r="I92" t="n">
-        <v>223</v>
-      </c>
-      <c r="J92" t="n">
-        <v>12</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-6.718336</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-79.770183</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>JUAN MEJIA BACA - CHICLAYO</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-6.7706</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-79.84332999999999</v>
-      </c>
-      <c r="I93" t="n">
-        <v>488</v>
-      </c>
-      <c r="J93" t="n">
-        <v>24</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-6.7706</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-79.84333</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>BLAS PASCAL</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-6.77123</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-79.83634000000001</v>
-      </c>
-      <c r="I94" t="n">
-        <v>252</v>
-      </c>
-      <c r="J94" t="n">
-        <v>15</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-6.77123</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-79.83634</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>10004</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-6.76829</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-79.83018</v>
-      </c>
-      <c r="I95" t="n">
-        <v>714</v>
-      </c>
-      <c r="J95" t="n">
-        <v>30</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-6.76829</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-79.83018</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>OLIVOS</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-6.78807</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-79.87043</v>
-      </c>
-      <c r="I96" t="n">
-        <v>33</v>
-      </c>
-      <c r="J96" t="n">
-        <v>2</v>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-6.78807</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-79.87043</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>TRILCE CHICLAYO</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-6.78293</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-79.84584</v>
-      </c>
-      <c r="I97" t="n">
-        <v>439</v>
-      </c>
-      <c r="J97" t="n">
-        <v>24</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-6.78293</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-79.84584</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>ESLID</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-6.78403</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-79.86635</v>
-      </c>
-      <c r="I98" t="n">
-        <v>220</v>
-      </c>
-      <c r="J98" t="n">
-        <v>16</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-6.78403</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-79.86635</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-6.771505</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-79.838662</v>
-      </c>
-      <c r="I99" t="n">
-        <v>200</v>
-      </c>
-      <c r="J99" t="n">
-        <v>14</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-6.771505</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-79.838662</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>EMPRENDEDORES GAJEL</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-6.769501</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-79.842747</v>
-      </c>
-      <c r="I100" t="n">
-        <v>333</v>
-      </c>
-      <c r="J100" t="n">
-        <v>14</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-6.769501</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-79.842747</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>FUTURA SCHOOLS</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-6.80109</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-79.88030000000001</v>
-      </c>
-      <c r="I101" t="n">
-        <v>333</v>
-      </c>
-      <c r="J101" t="n">
-        <v>21</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-6.80109</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-79.8803</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>PERUANO ESPAÑOL INTER MUNDO</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-6.77063</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-79.83521</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1426</v>
-      </c>
-      <c r="J102" t="n">
-        <v>69</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-6.77063</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-79.83521</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>11513 JUAN PARDO Y MIGUEL</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-6.7376</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-79.64100000000001</v>
-      </c>
-      <c r="I103" t="n">
-        <v>390</v>
-      </c>
-      <c r="J103" t="n">
-        <v>20</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-6.7376</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-79.641</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>EMPRENDEDORES GAJEL</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-6.77666</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-79.84529999999999</v>
-      </c>
-      <c r="I104" t="n">
-        <v>812</v>
-      </c>
-      <c r="J104" t="n">
-        <v>16</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-6.77666</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-79.8453</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>56266</t>
+          <t>275551</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>G.M.V. COLLEGE / LUCERITOS DEL SABER / PINCELADAS DE COLORES</t>
+          <t>031 ANGELITOS DEL CIELO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.78453</t>
+          <t>-6.7705</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.86287</t>
+          <t>-79.871</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57671</t>
+          <t>276169</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRILCE CHICLAYO</t>
+          <t>015 SANTA MARIA DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.78336</t>
+          <t>-6.77141</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.84588</t>
+          <t>-79.86599</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>275438</t>
+          <t>673550</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11004 SAN PEDRO</t>
+          <t>JOYITAS DE JESUS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.760561</t>
+          <t>-6.718336</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.855511</t>
+          <t>-79.770183</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>275443</t>
+          <t>275928</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>003 LOS PASTORCITOS DE LA VIRGEN DE FATIMA</t>
+          <t>11003 KARL WEISS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.7642</t>
+          <t>-6.77517</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.8279</t>
+          <t>-79.83092</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>275457</t>
+          <t>507768</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>004 ANGELITOS DE MARIA</t>
+          <t>JUAN MEJIA BACA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.7787</t>
+          <t>-6.77562</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.8346</t>
+          <t>-79.83226</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>705</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>275495</t>
+          <t>754990</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10021 SAN JOSE</t>
+          <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.774947</t>
+          <t>-6.771505</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.847868</t>
+          <t>-79.838662</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>275527</t>
+          <t>810161</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>022 COSOMITO</t>
+          <t>EMPRENDEDORES GAJEL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.76708</t>
+          <t>-6.769501</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.84975</t>
+          <t>-79.842747</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>275551</t>
+          <t>56266</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>031 ANGELITOS DEL CIELO</t>
+          <t>G.M.V. COLLEGE / LUCERITOS DEL SABER / PINCELADAS DE COLORES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.7705</t>
+          <t>-6.78453</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.871</t>
+          <t>-79.86287</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>275612</t>
+          <t>275443</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>048 SEMILLLITAS DE JESUS</t>
+          <t>003 LOS PASTORCITOS DE LA VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.76523</t>
+          <t>-6.7642</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.84604</t>
+          <t>-79.8279</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>386</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>275626</t>
+          <t>275457</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>049 VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>004 ANGELITOS DE MARIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.78322</t>
+          <t>-6.7787</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.83533</t>
+          <t>-79.8346</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>275631</t>
+          <t>280996</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>002 MARAVILLAS DE JESUS</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.7841</t>
+          <t>-6.7441</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.84052</t>
+          <t>-79.5416</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>306</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>275650</t>
+          <t>673606</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>119 FELIPE ALVA Y ALVA</t>
+          <t>BLAS PASCAL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.75915</t>
+          <t>-6.77123</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.85954</t>
+          <t>-79.83634</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>275669</t>
+          <t>275749</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>121 NUESTRA SEÑORA DEL PILAR</t>
+          <t>10026 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.77958</t>
+          <t>-6.77844</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.86658</t>
+          <t>-79.84301</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>275688</t>
+          <t>281415</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11223 FELIX TELLO ROJAS</t>
+          <t>11589 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.76423</t>
+          <t>-6.6918</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.85515</t>
+          <t>-79.7037</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>275706</t>
+          <t>715885</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>ESLID</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.778622</t>
+          <t>-6.78403</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.867817</t>
+          <t>-79.86635</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>275711</t>
+          <t>860028</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>EMPRENDEDORES GAJEL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.76731</t>
+          <t>-6.77666</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.83222</t>
+          <t>-79.8453</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>812</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>275730</t>
+          <t>275527</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10024 NUESTRA SEÑORA DE FATIMA</t>
+          <t>022 COSOMITO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.777221</t>
+          <t>-6.76708</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.84843</t>
+          <t>-79.84975</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>431</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>275749</t>
+          <t>275773</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10026 SAN MARTIN DE PORRES</t>
+          <t>10223 RICARDO PALMA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.77844</t>
+          <t>-6.76661</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.84301</t>
+          <t>-79.85937</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>275754</t>
+          <t>279078</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10040 SANTIAGO CASSINELLI CHIAPPE</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.76347</t>
+          <t>-6.816828</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.84465</t>
+          <t>-79.85383</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>275768</t>
+          <t>612217</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10042 MONSEÑOR JUAN TOMIS STACK</t>
+          <t>PAUL HARRIS COLLEGE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.76565</t>
+          <t>-6.77066</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.856812</t>
+          <t>-79.84223</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,27 +1741,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>275773</t>
+          <t>673319</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10223 RICARDO PALMA</t>
+          <t>FREDERICK SANGER</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.76661</t>
+          <t>-6.789298</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.85937</t>
+          <t>-79.850353</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>275787</t>
+          <t>277116</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11001 LEONCIO PRADO</t>
+          <t>ADVENTISTA CHICLAYO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.76989</t>
+          <t>-6.76707</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.83103</t>
+          <t>-79.84105</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>275792</t>
+          <t>280604</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>11006 RAMON ESPINOZA SIERRA / RAMON ESPINOZA SIERRA</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.76582</t>
+          <t>-6.9216</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.84587</t>
+          <t>-79.5863</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>275829</t>
+          <t>507891</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11014 INMACULADA CONCEPCION</t>
+          <t>UNIVERSIA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.78359</t>
+          <t>-6.76965</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.83574</t>
+          <t>-79.83353</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>275834</t>
+          <t>275438</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11015 COMANDANTE ELIAS AGUIRRE</t>
+          <t>11004 SAN PEDRO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.77085</t>
+          <t>-6.760561</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.83813</t>
+          <t>-79.855511</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>469</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>275848</t>
+          <t>275631</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>11016 JUAN MEJIA BACA</t>
+          <t>002 MARAVILLAS DE JESUS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.77697</t>
+          <t>-6.7841</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.8476</t>
+          <t>-79.84052</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>479</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>275853</t>
+          <t>275914</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>11017 NICOLAS LA TORRE GARCIA</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.77065</t>
+          <t>-6.77918</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.84687</t>
+          <t>-79.84684</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>275886</t>
+          <t>571207</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11023 ABRAHAM VALDELOMAR</t>
+          <t>030 VICTORIA SILVA DE DALL'ORSO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-6.77101</t>
+          <t>-6.77464</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.85279</t>
+          <t>-79.84671</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>467</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,42 +2237,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>275891</t>
+          <t>675865</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>11024 JOSE QUIÑONES GONZALES</t>
+          <t>OLIVOS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.77157</t>
+          <t>-6.78807</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.86826</t>
+          <t>-79.87043</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>275909</t>
+          <t>57671</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>TRILCE CHICLAYO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6.77219</t>
+          <t>-6.78336</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-79.84822</t>
+          <t>-79.84588</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>275914</t>
+          <t>275626</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>049 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-6.77918</t>
+          <t>-6.78322</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.84684</t>
+          <t>-79.83533</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>275928</t>
+          <t>838730</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11003 KARL WEISS</t>
+          <t>11513 JUAN PARDO Y MIGUEL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.77517</t>
+          <t>-6.7376</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.83092</t>
+          <t>-79.641</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>390</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>275933</t>
+          <t>276824</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>SANTA LUCIA SCHOOL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.773036</t>
+          <t>-6.77243</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.864398</t>
+          <t>-79.86939</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>162</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>275947</t>
+          <t>612986</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.76905</t>
+          <t>-6.77441</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.87049</t>
+          <t>-79.83539</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>275952</t>
+          <t>616159</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10925 CESAR VALLEJO / CESAR VALLEJO</t>
+          <t>CRECIENDO CON AMOR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-6.76145</t>
+          <t>-6.78444</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-79.8254</t>
+          <t>-79.84452</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>314</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>275971</t>
+          <t>811684</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11051 MARIA REICHE</t>
+          <t>FUTURA SCHOOLS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-6.76593</t>
+          <t>-6.80109</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-79.8259</t>
+          <t>-79.8803</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>275990</t>
+          <t>275495</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10021 SAN JOSE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-6.76624</t>
+          <t>-6.774947</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-79.82217</t>
+          <t>-79.847868</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>216</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>276008</t>
+          <t>275971</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>11124 NUESTRA SEÑORA DE LA PAZ</t>
+          <t>11051 MARIA REICHE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-6.78063</t>
+          <t>-6.76593</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-79.8647</t>
+          <t>-79.8259</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>595</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>276013</t>
+          <t>277178</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>11151 MONSEÑOR AUGUSTO VARGAS ALZAMORA</t>
+          <t>SAN GABRIEL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-6.76049</t>
+          <t>-6.76578</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-79.85934</t>
+          <t>-79.84161</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>276032</t>
+          <t>277197</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ROSA FLORES DE OLIVA</t>
+          <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.76938</t>
+          <t>-6.77435</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-79.86447</t>
+          <t>-79.83708</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>276046</t>
+          <t>278875</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PEDRO ABEL LABARTHE DURAND</t>
+          <t>MANUEL ANTONIO RIVAS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.77495</t>
+          <t>-6.75605</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-79.84011</t>
+          <t>-79.84058</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>306</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>276094</t>
+          <t>673277</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>AMIGOS SCHOOL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.7819</t>
+          <t>-6.76637</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-79.8361</t>
+          <t>-79.83688</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,37 +3105,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>276107</t>
+          <t>275754</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SANTA MAGDALENA SOFIA</t>
+          <t>10040 SANTIAGO CASSINELLI CHIAPPE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-6.77077</t>
+          <t>-6.76347</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-79.84768</t>
+          <t>-79.84465</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>499</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>276112</t>
+          <t>279097</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-6.7592</t>
+          <t>-6.82902</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-79.8585</t>
+          <t>-79.87584</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>436</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>276145</t>
+          <t>280963</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10825 JUAN XXIII</t>
+          <t>GREGORIO ODAR MORE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-6.7741</t>
+          <t>-6.7445</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-79.8694</t>
+          <t>-79.5417</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>276169</t>
+          <t>673593</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>015 SANTA MARIA DE LOS NIÑOS</t>
+          <t>JUAN MEJIA BACA - CHICLAYO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-6.77141</t>
+          <t>-6.7706</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-79.86599</t>
+          <t>-79.84333</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>488</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>276188</t>
+          <t>706739</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MANUEL PARDO</t>
+          <t>TRILCE CHICLAYO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-6.765613</t>
+          <t>-6.78293</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-79.842326</t>
+          <t>-79.84584</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>439</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>276193</t>
+          <t>276145</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BEATA IMELDA</t>
+          <t>10825 JUAN XXIII</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-6.76905</t>
+          <t>-6.7741</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-79.83877</t>
+          <t>-79.8694</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>640</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>276211</t>
+          <t>555957</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SANTA ANGELA</t>
+          <t>DEPORTIVO ADEU</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-6.78799</t>
+          <t>-6.77239</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-79.84678</t>
+          <t>-79.840628</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>287</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>276225</t>
+          <t>673512</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SANTA MARIA REINA</t>
+          <t>UN NUEVO TUMAN</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-6.78525</t>
+          <t>-6.750425</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-79.84646</t>
+          <t>-79.703452</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,37 +3601,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>276254</t>
+          <t>276758</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-6.7688</t>
+          <t>-6.76912</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-79.84683</t>
+          <t>-79.84189</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>349</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>276292</t>
+          <t>276013</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CAPITAN FAP RENAN ELIAS OLIVERA</t>
+          <t>11151 MONSEÑOR AUGUSTO VARGAS ALZAMORA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-6.77548</t>
+          <t>-6.76049</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-79.82107</t>
+          <t>-79.85934</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>620</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>276348</t>
+          <t>275848</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 28</t>
+          <t>11016 JUAN MEJIA BACA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-6.77826</t>
+          <t>-6.77697</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-79.86399</t>
+          <t>-79.8476</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>420</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>276391</t>
+          <t>552317</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ROSA MARIA CHECA</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-6.77057</t>
+          <t>-6.78558</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-79.86144</t>
+          <t>-79.86507</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>397</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>276758</t>
+          <t>275706</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-6.76912</t>
+          <t>-6.778622</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-79.84189</t>
+          <t>-79.867817</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>669</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>276824</t>
+          <t>275787</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SANTA LUCIA SCHOOL</t>
+          <t>11001 LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-6.77243</t>
+          <t>-6.76989</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-79.86939</t>
+          <t>-79.83103</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>586</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>277098</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>ROSA MARIA CHECA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-6.77318</t>
+          <t>-6.77057</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-79.83649</t>
+          <t>-79.86144</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>384</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>277116</t>
+          <t>275711</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ADVENTISTA CHICLAYO</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-6.76707</t>
+          <t>-6.76731</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-79.84105</t>
+          <t>-79.83222</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>814</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>277178</t>
+          <t>673673</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SAN GABRIEL</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-6.76578</t>
+          <t>-6.76829</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-79.84161</t>
+          <t>-79.83018</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>714</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>277197</t>
+          <t>275834</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO</t>
+          <t>11015 COMANDANTE ELIAS AGUIRRE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-6.77435</t>
+          <t>-6.77085</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-79.83708</t>
+          <t>-79.83813</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>805</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>277376</t>
+          <t>275891</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>JORGE BASADRE</t>
+          <t>11024 JOSE QUIÑONES GONZALES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-6.77088</t>
+          <t>-6.77157</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-79.83678</t>
+          <t>-79.86826</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>744</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>277593</t>
+          <t>397034</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>APPUL COLLEGE</t>
+          <t>COAR LAMBAYEQUE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-6.77401</t>
+          <t>-6.776861</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-79.84325</t>
+          <t>-79.847033</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>292</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>277710</t>
+          <t>275792</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FLEMING COLLEGE</t>
+          <t>11006 RAMON ESPINOZA SIERRA / RAMON ESPINOZA SIERRA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-6.76605</t>
+          <t>-6.76582</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-79.82637</t>
+          <t>-79.84587</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>758</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>278352</t>
+          <t>281156</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11027 DIVINO NIÑO DEL MILAGRO</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-6.90712</t>
+          <t>-6.770031</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-79.86003</t>
+          <t>-79.77616</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>683</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>278385</t>
+          <t>275886</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PEDRO RUIZ GALLO</t>
+          <t>11023 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-6.9075</t>
+          <t>-6.77101</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-79.85924</t>
+          <t>-79.85279</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>790</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>278521</t>
+          <t>278352</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>024 LA INMACULADA</t>
+          <t>11027 DIVINO NIÑO DEL MILAGRO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-6.75102</t>
+          <t>-6.90712</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-79.83652</t>
+          <t>-79.86003</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>957</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>278875</t>
+          <t>275730</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MANUEL ANTONIO RIVAS</t>
+          <t>10024 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-6.75605</t>
+          <t>-6.777221</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-79.84058</t>
+          <t>-79.84843</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>760</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>279078</t>
+          <t>276112</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-6.816828</t>
+          <t>-6.7592</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-79.85383</t>
+          <t>-79.8585</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>279097</t>
+          <t>280958</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>JOSE DOMINGO ATOCHE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-6.82902</t>
+          <t>-6.7362</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-79.87584</t>
+          <t>-79.6407</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>587</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>279766</t>
+          <t>275688</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE</t>
+          <t>11223 FELIX TELLO ROJAS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-6.772027</t>
+          <t>-6.76423</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-79.832035</t>
+          <t>-79.85515</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>787</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>280294</t>
+          <t>275933</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ALGARROBOS</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-6.800517</t>
+          <t>-6.773036</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-79.880573</t>
+          <t>-79.864398</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>875</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>280604</t>
+          <t>278385</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-6.9216</t>
+          <t>-6.9075</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-79.5863</t>
+          <t>-79.85924</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>813</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>280958</t>
+          <t>277710</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JOSE DOMINGO ATOCHE</t>
+          <t>FLEMING COLLEGE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-6.7362</t>
+          <t>-6.76605</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-79.6407</t>
+          <t>-79.82637</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>865</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>280963</t>
+          <t>275952</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GREGORIO ODAR MORE</t>
+          <t>10925 CESAR VALLEJO / CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-6.7445</t>
+          <t>-6.76145</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-79.5417</t>
+          <t>-79.8254</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>687</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>280996</t>
+          <t>277593</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>APPUL COLLEGE</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-6.7441</t>
+          <t>-6.77401</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-79.5416</t>
+          <t>-79.84325</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>281156</t>
+          <t>275909</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-6.770031</t>
+          <t>-6.77219</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-79.77616</t>
+          <t>-79.84822</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>281415</t>
+          <t>276292</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>11589 JUAN VELASCO ALVARADO</t>
+          <t>CAPITAN FAP RENAN ELIAS OLIVERA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-6.6918</t>
+          <t>-6.77548</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-79.7037</t>
+          <t>-79.82107</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>397034</t>
+          <t>275947</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>COAR LAMBAYEQUE</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-6.776861</t>
+          <t>-6.76905</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-79.847033</t>
+          <t>-79.87049</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>995</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5337,37 +5337,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>507768</t>
+          <t>275853</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>JUAN MEJIA BACA</t>
+          <t>11017 NICOLAS LA TORRE GARCIA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-6.77562</t>
+          <t>-6.77065</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-79.83226</t>
+          <t>-79.84687</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>507891</t>
+          <t>276008</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UNIVERSIA</t>
+          <t>11124 NUESTRA SEÑORA DE LA PAZ</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-6.76965</t>
+          <t>-6.78063</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-79.83353</t>
+          <t>-79.8647</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>552317</t>
+          <t>277098</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-6.78558</t>
+          <t>-6.77318</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-79.86507</t>
+          <t>-79.83649</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,37 +5523,37 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>555957</t>
+          <t>276254</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>DEPORTIVO ADEU</t>
+          <t>CHICLAYO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-6.77239</t>
+          <t>-6.7688</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-79.840628</t>
+          <t>-79.84683</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>571207</t>
+          <t>276211</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>030 VICTORIA SILVA DE DALL'ORSO</t>
+          <t>SANTA ANGELA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-6.77464</t>
+          <t>-6.78799</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-79.84671</t>
+          <t>-79.84678</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>736</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>612217</t>
+          <t>280294</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PAUL HARRIS COLLEGE</t>
+          <t>ALGARROBOS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-6.77066</t>
+          <t>-6.800517</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-79.84223</t>
+          <t>-79.880573</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>620</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>612986</t>
+          <t>276193</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MARIO VARGAS LLOSA</t>
+          <t>BEATA IMELDA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-6.77441</t>
+          <t>-6.76905</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-79.83539</t>
+          <t>-79.83877</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>450</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>616159</t>
+          <t>279766</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CRECIENDO CON AMOR</t>
+          <t>PERUANO CANADIENSE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-6.78444</t>
+          <t>-6.772027</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-79.84452</t>
+          <t>-79.832035</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,37 +5833,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>673277</t>
+          <t>277376</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AMIGOS SCHOOL</t>
+          <t>JORGE BASADRE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-6.76637</t>
+          <t>-6.77088</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-79.83688</t>
+          <t>-79.83678</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>673319</t>
+          <t>276094</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FREDERICK SANGER</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-6.789298</t>
+          <t>-6.7819</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-79.850353</t>
+          <t>-79.8361</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>673357</t>
+          <t>276348</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MATER ADMIRABILIS</t>
+          <t>FE Y ALEGRIA 28</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-6.750883</t>
+          <t>-6.77826</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-79.840113</t>
+          <t>-79.86399</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>673512</t>
+          <t>823899</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UN NUEVO TUMAN</t>
+          <t>PERUANO ESPAÑOL INTER MUNDO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-6.750425</t>
+          <t>-6.77063</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-79.703452</t>
+          <t>-79.83521</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>673550</t>
+          <t>276107</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JOYITAS DE JESUS</t>
+          <t>SANTA MAGDALENA SOFIA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-6.718336</t>
+          <t>-6.77077</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-79.770183</t>
+          <t>-79.84768</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>673593</t>
+          <t>673357</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JUAN MEJIA BACA - CHICLAYO</t>
+          <t>MATER ADMIRABILIS</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-6.7706</t>
+          <t>-6.750883</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-79.84333</t>
+          <t>-79.840113</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>673606</t>
+          <t>276032</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BLAS PASCAL</t>
+          <t>ROSA FLORES DE OLIVA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-6.77123</t>
+          <t>-6.76938</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-79.83634</t>
+          <t>-79.86447</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>673673</t>
+          <t>275768</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10042 MONSEÑOR JUAN TOMIS STACK</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-6.76829</t>
+          <t>-6.76565</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-79.83018</t>
+          <t>-79.856812</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6329,42 +6329,42 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>675865</t>
+          <t>276188</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>OLIVOS</t>
+          <t>MANUEL PARDO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-6.78807</t>
+          <t>-6.765613</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-79.87043</t>
+          <t>-79.842326</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>706739</t>
+          <t>275990</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>TRILCE CHICLAYO</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-6.78293</t>
+          <t>-6.76624</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-79.84584</t>
+          <t>-79.82217</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>715885</t>
+          <t>275829</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ESLID</t>
+          <t>11014 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-6.78403</t>
+          <t>-6.78359</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-79.86635</t>
+          <t>-79.83574</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>754990</t>
+          <t>276225</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN</t>
+          <t>SANTA MARIA REINA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-6.771505</t>
+          <t>-6.78525</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-79.838662</t>
+          <t>-79.84646</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>810161</t>
+          <t>275612</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>EMPRENDEDORES GAJEL</t>
+          <t>048 SEMILLLITAS DE JESUS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-6.769501</t>
+          <t>-6.76523</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-79.842747</t>
+          <t>-79.84604</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>811684</t>
+          <t>275650</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS</t>
+          <t>119 FELIPE ALVA Y ALVA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-6.80109</t>
+          <t>-6.75915</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-79.8803</t>
+          <t>-79.85954</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>823899</t>
+          <t>275669</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PERUANO ESPAÑOL INTER MUNDO</t>
+          <t>121 NUESTRA SEÑORA DEL PILAR</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-6.77063</t>
+          <t>-6.77958</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-79.83521</t>
+          <t>-79.86658</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>838730</t>
+          <t>278521</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>11513 JUAN PARDO Y MIGUEL</t>
+          <t>024 LA INMACULADA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-6.7376</t>
+          <t>-6.75102</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-79.641</t>
+          <t>-79.83652</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>860028</t>
+          <t>276046</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>EMPRENDEDORES GAJEL</t>
+          <t>PEDRO ABEL LABARTHE DURAND</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-6.77666</t>
+          <t>-6.77495</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-79.8453</t>
+          <t>-79.84011</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>275551</t>
+          <t>860028</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>031 ANGELITOS DEL CIELO</t>
+          <t>EMPRENDEDORES GAJEL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.7705</t>
+          <t>812</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.871</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-6.77666</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.8453</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>276169</t>
+          <t>838730</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>015 SANTA MARIA DE LOS NIÑOS</t>
+          <t>11513 JUAN PARDO Y MIGUEL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.77141</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.86599</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-6.7376</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.641</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>673550</t>
+          <t>823899</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JOYITAS DE JESUS</t>
+          <t>PERUANO ESPAÑOL INTER MUNDO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.718336</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.770183</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>-6.77063</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-79.83521</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>275928</t>
+          <t>811684</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11003 KARL WEISS</t>
+          <t>FUTURA SCHOOLS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.77517</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.83092</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>-6.80109</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>-79.8803</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>507768</t>
+          <t>810161</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JUAN MEJIA BACA</t>
+          <t>EMPRENDEDORES GAJEL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.77562</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.83226</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>-6.769501</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.842747</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>-6.771505</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>-79.838662</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>810161</t>
+          <t>715885</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EMPRENDEDORES GAJEL</t>
+          <t>ESLID</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.769501</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.842747</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-6.78403</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.86635</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>56266</t>
+          <t>706739</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>G.M.V. COLLEGE / LUCERITOS DEL SABER / PINCELADAS DE COLORES</t>
+          <t>TRILCE CHICLAYO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.78453</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.86287</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-6.78293</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.84584</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>275443</t>
+          <t>675865</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>003 LOS PASTORCITOS DE LA VIRGEN DE FATIMA</t>
+          <t>OLIVOS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.7642</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.8279</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>-6.78807</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.87043</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>275457</t>
+          <t>673673</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>004 ANGELITOS DE MARIA</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.7787</t>
+          <t>714</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.8346</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-6.76829</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.83018</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>280996</t>
+          <t>673606</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>BLAS PASCAL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.7441</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.5416</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>-6.77123</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.83634</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>673606</t>
+          <t>673593</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BLAS PASCAL</t>
+          <t>JUAN MEJIA BACA - CHICLAYO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.77123</t>
+          <t>488</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.83634</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-6.7706</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.84333</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>275749</t>
+          <t>673550</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10026 SAN MARTIN DE PORRES</t>
+          <t>JOYITAS DE JESUS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.77844</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.84301</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>-6.718336</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.770183</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>281415</t>
+          <t>673512</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11589 JUAN VELASCO ALVARADO</t>
+          <t>UN NUEVO TUMAN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.6918</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.7037</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-6.750425</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.703452</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>715885</t>
+          <t>673357</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ESLID</t>
+          <t>MATER ADMIRABILIS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.78403</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.86635</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-6.750883</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.840113</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>860028</t>
+          <t>673319</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EMPRENDEDORES GAJEL</t>
+          <t>FREDERICK SANGER</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.77666</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.8453</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>-6.789298</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.850353</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>275527</t>
+          <t>673277</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>022 COSOMITO</t>
+          <t>AMIGOS SCHOOL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.76708</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.84975</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>-6.76637</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.83688</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>275773</t>
+          <t>616159</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10223 RICARDO PALMA</t>
+          <t>CRECIENDO CON AMOR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.76661</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.85937</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>-6.78444</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.84452</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>279078</t>
+          <t>612986</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.816828</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.85383</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>-6.77441</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.83539</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1689,22 +1689,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>-6.77066</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-79.84223</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>673319</t>
+          <t>571207</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FREDERICK SANGER</t>
+          <t>030 VICTORIA SILVA DE DALL'ORSO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.789298</t>
+          <t>467</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.850353</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-6.77464</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.84671</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>277116</t>
+          <t>555957</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ADVENTISTA CHICLAYO</t>
+          <t>DEPORTIVO ADEU</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.76707</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.84105</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-6.77239</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.840628</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>280604</t>
+          <t>552317</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.9216</t>
+          <t>397</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.5863</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>-6.78558</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.86507</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1937,22 +1937,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>-6.76965</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>-79.83353</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>275438</t>
+          <t>507768</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11004 SAN PEDRO</t>
+          <t>JUAN MEJIA BACA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.760561</t>
+          <t>705</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.855511</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>-6.77562</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.83226</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>275631</t>
+          <t>397034</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>002 MARAVILLAS DE JESUS</t>
+          <t>COAR LAMBAYEQUE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.7841</t>
+          <t>292</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.84052</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>-6.776861</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.847033</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>275914</t>
+          <t>281415</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>11589 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.77918</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.84684</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-6.6918</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.7037</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>571207</t>
+          <t>281156</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>030 VICTORIA SILVA DE DALL'ORSO</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-6.77464</t>
+          <t>683</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.84671</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>-6.770031</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.77616</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,42 +2237,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>675865</t>
+          <t>280996</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OLIVOS</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.78807</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.87043</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-6.7441</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-79.5416</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>57671</t>
+          <t>280963</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TRILCE CHICLAYO</t>
+          <t>GREGORIO ODAR MORE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6.78336</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-79.84588</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-6.7445</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.5417</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>275626</t>
+          <t>280958</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>049 VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>JOSE DOMINGO ATOCHE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-6.78322</t>
+          <t>587</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.83533</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>-6.7362</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.6407</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>838730</t>
+          <t>280604</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11513 JUAN PARDO Y MIGUEL</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.7376</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.641</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>-6.9216</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.5863</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>276824</t>
+          <t>280294</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SANTA LUCIA SCHOOL</t>
+          <t>ALGARROBOS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.77243</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.86939</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>-6.800517</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.880573</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>612986</t>
+          <t>279766</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MARIO VARGAS LLOSA</t>
+          <t>PERUANO CANADIENSE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.77441</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.83539</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-6.772027</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.832035</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>616159</t>
+          <t>279097</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CRECIENDO CON AMOR</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-6.78444</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-79.84452</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>-6.82902</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.87584</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>811684</t>
+          <t>279078</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-6.80109</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-79.8803</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-6.816828</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.85383</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>275495</t>
+          <t>278875</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10021 SAN JOSE</t>
+          <t>MANUEL ANTONIO RIVAS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-6.774947</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-79.847868</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>-6.75605</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-79.84058</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>275971</t>
+          <t>278521</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>11051 MARIA REICHE</t>
+          <t>024 LA INMACULADA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-6.76593</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-79.8259</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>-6.75102</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.83652</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>277178</t>
+          <t>278385</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN GABRIEL</t>
+          <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-6.76578</t>
+          <t>813</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-79.84161</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-6.9075</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.85924</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>277197</t>
+          <t>278352</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO</t>
+          <t>11027 DIVINO NIÑO DEL MILAGRO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.77435</t>
+          <t>957</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-79.83708</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-6.90712</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.86003</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>278875</t>
+          <t>277710</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MANUEL ANTONIO RIVAS</t>
+          <t>FLEMING COLLEGE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.75605</t>
+          <t>865</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-79.84058</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>-6.76605</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.82637</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>673277</t>
+          <t>277593</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AMIGOS SCHOOL</t>
+          <t>APPUL COLLEGE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.76637</t>
+          <t>762</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-79.83688</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-6.77401</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.84325</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>275754</t>
+          <t>277376</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10040 SANTIAGO CASSINELLI CHIAPPE</t>
+          <t>JORGE BASADRE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-6.76347</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-79.84465</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>-6.77088</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.83678</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>279097</t>
+          <t>277197</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-6.82902</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-79.87584</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>-6.77435</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.83708</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>280963</t>
+          <t>277178</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GREGORIO ODAR MORE</t>
+          <t>SAN GABRIEL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-6.7445</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-79.5417</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-6.76578</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.84161</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>673593</t>
+          <t>277116</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JUAN MEJIA BACA - CHICLAYO</t>
+          <t>ADVENTISTA CHICLAYO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-6.7706</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-79.84333</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>-6.76707</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.84105</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>706739</t>
+          <t>277098</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TRILCE CHICLAYO</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-6.78293</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-79.84584</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>-6.77318</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.83649</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>276145</t>
+          <t>276824</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10825 JUAN XXIII</t>
+          <t>SANTA LUCIA SCHOOL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-6.7741</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-79.8694</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>-6.77243</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-79.86939</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>555957</t>
+          <t>276758</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DEPORTIVO ADEU</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-6.77239</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-79.840628</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>-6.76912</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-79.84189</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>673512</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UN NUEVO TUMAN</t>
+          <t>ROSA MARIA CHECA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-6.750425</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-79.703452</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>-6.77057</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-79.86144</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>276758</t>
+          <t>276348</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>FE Y ALEGRIA 28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-6.76912</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-79.84189</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>-6.77826</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.86399</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>276013</t>
+          <t>276292</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>11151 MONSEÑOR AUGUSTO VARGAS ALZAMORA</t>
+          <t>CAPITAN FAP RENAN ELIAS OLIVERA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-6.76049</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-79.85934</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>-6.77548</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.82107</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,42 +3725,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>275848</t>
+          <t>276254</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>11016 JUAN MEJIA BACA</t>
+          <t>CHICLAYO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-6.77697</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-79.8476</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>-6.7688</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-79.84683</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>552317</t>
+          <t>276225</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>SANTA MARIA REINA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-6.78558</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-79.86507</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>-6.78525</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-79.84646</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>275706</t>
+          <t>276211</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>SANTA ANGELA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-6.778622</t>
+          <t>736</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-79.867817</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>-6.78799</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.84678</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>275787</t>
+          <t>276193</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>11001 LEONCIO PRADO</t>
+          <t>BEATA IMELDA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-6.76989</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-79.83103</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>-6.76905</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.83877</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>276391</t>
+          <t>276188</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ROSA MARIA CHECA</t>
+          <t>MANUEL PARDO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-6.77057</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-79.86144</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>-6.765613</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.842326</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>275711</t>
+          <t>276169</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>015 SANTA MARIA DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-6.76731</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-79.83222</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>-6.77141</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.86599</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>673673</t>
+          <t>276145</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10825 JUAN XXIII</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-6.76829</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-79.83018</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>-6.7741</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.8694</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>275834</t>
+          <t>276112</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>11015 COMANDANTE ELIAS AGUIRRE</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-6.77085</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-79.83813</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>-6.7592</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-79.8585</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>275891</t>
+          <t>276107</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>11024 JOSE QUIÑONES GONZALES</t>
+          <t>SANTA MAGDALENA SOFIA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-6.77157</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-79.86826</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>-6.77077</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-79.84768</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>397034</t>
+          <t>276094</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>COAR LAMBAYEQUE</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-6.776861</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-79.847033</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>-6.7819</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-79.8361</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>275792</t>
+          <t>276046</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>11006 RAMON ESPINOZA SIERRA / RAMON ESPINOZA SIERRA</t>
+          <t>PEDRO ABEL LABARTHE DURAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-6.76582</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-79.84587</t>
+          <t>96</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>-6.77495</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-79.84011</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>281156</t>
+          <t>276032</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>ROSA FLORES DE OLIVA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-6.770031</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-79.77616</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>-6.76938</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-79.86447</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>275886</t>
+          <t>276013</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>11023 ABRAHAM VALDELOMAR</t>
+          <t>11151 MONSEÑOR AUGUSTO VARGAS ALZAMORA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-6.77101</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-79.85279</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>-6.76049</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.85934</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>278352</t>
+          <t>276008</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11027 DIVINO NIÑO DEL MILAGRO</t>
+          <t>11124 NUESTRA SEÑORA DE LA PAZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-6.90712</t>
+          <t>762</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-79.86003</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>-6.78063</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-79.8647</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>275730</t>
+          <t>275990</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10024 NUESTRA SEÑORA DE FATIMA</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-6.777221</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-79.84843</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>-6.76624</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.82217</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>276112</t>
+          <t>275971</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>11051 MARIA REICHE</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-6.7592</t>
+          <t>595</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-79.8585</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>-6.76593</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.8259</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>280958</t>
+          <t>275952</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JOSE DOMINGO ATOCHE</t>
+          <t>10925 CESAR VALLEJO / CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-6.7362</t>
+          <t>687</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-79.6407</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>-6.76145</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.8254</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>275688</t>
+          <t>275947</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>11223 FELIX TELLO ROJAS</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-6.76423</t>
+          <t>995</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-79.85515</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>-6.76905</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-79.87049</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4851,22 +4851,22 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
           <t>-6.773036</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>-79.864398</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>875</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>278385</t>
+          <t>275928</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PEDRO RUIZ GALLO</t>
+          <t>11003 KARL WEISS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-6.9075</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-79.85924</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>-6.77517</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-79.83092</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>277710</t>
+          <t>275914</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FLEMING COLLEGE</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-6.76605</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-79.82637</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>-6.77918</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-79.84684</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>275952</t>
+          <t>275909</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>10925 CESAR VALLEJO / CESAR VALLEJO</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-6.76145</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-79.8254</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>-6.77219</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-79.84822</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>277593</t>
+          <t>275891</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>APPUL COLLEGE</t>
+          <t>11024 JOSE QUIÑONES GONZALES</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-6.77401</t>
+          <t>744</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-79.84325</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>-6.77157</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-79.86826</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>275909</t>
+          <t>275886</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>11023 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-6.77219</t>
+          <t>790</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-79.84822</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>-6.77101</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-79.85279</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,37 +5213,37 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>276292</t>
+          <t>275853</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CAPITAN FAP RENAN ELIAS OLIVERA</t>
+          <t>11017 NICOLAS LA TORRE GARCIA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-6.77548</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-79.82107</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>-6.77065</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-79.84687</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>275947</t>
+          <t>275848</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>11016 JUAN MEJIA BACA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-6.76905</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-79.87049</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>-6.77697</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-79.8476</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5337,37 +5337,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>275853</t>
+          <t>275834</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>11017 NICOLAS LA TORRE GARCIA</t>
+          <t>11015 COMANDANTE ELIAS AGUIRRE</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-6.77065</t>
+          <t>805</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-79.84687</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>-6.77085</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-79.83813</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>276008</t>
+          <t>275829</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>11124 NUESTRA SEÑORA DE LA PAZ</t>
+          <t>11014 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-6.78063</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-79.8647</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>-6.78359</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-79.83574</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>277098</t>
+          <t>275792</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>11006 RAMON ESPINOZA SIERRA / RAMON ESPINOZA SIERRA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-6.77318</t>
+          <t>758</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-79.83649</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>-6.76582</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-79.84587</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,37 +5523,37 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>276254</t>
+          <t>275787</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>11001 LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-6.7688</t>
+          <t>586</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-79.84683</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-6.76989</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-79.83103</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>276211</t>
+          <t>275773</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SANTA ANGELA</t>
+          <t>10223 RICARDO PALMA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-6.78799</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-79.84678</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>-6.76661</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-79.85937</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>280294</t>
+          <t>275768</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ALGARROBOS</t>
+          <t>10042 MONSEÑOR JUAN TOMIS STACK</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-6.800517</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-79.880573</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>-6.76565</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-79.856812</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>276193</t>
+          <t>275754</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BEATA IMELDA</t>
+          <t>10040 SANTIAGO CASSINELLI CHIAPPE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-6.76905</t>
+          <t>499</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-79.83877</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>-6.76347</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-79.84465</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>279766</t>
+          <t>275749</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE</t>
+          <t>10026 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-6.772027</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-79.832035</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>-6.77844</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-79.84301</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>277376</t>
+          <t>275730</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>JORGE BASADRE</t>
+          <t>10024 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-6.77088</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-79.83678</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>-6.777221</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-79.84843</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>276094</t>
+          <t>275711</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-6.7819</t>
+          <t>814</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-79.8361</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>-6.76731</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-79.83222</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>276348</t>
+          <t>275706</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 28</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-6.77826</t>
+          <t>669</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-79.86399</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>-6.778622</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-79.867817</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>823899</t>
+          <t>275688</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PERUANO ESPAÑOL INTER MUNDO</t>
+          <t>11223 FELIX TELLO ROJAS</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-6.77063</t>
+          <t>787</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-79.83521</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>-6.76423</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-79.85515</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>276107</t>
+          <t>275669</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SANTA MAGDALENA SOFIA</t>
+          <t>121 NUESTRA SEÑORA DEL PILAR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-6.77077</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-79.84768</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>-6.77958</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-79.86658</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>673357</t>
+          <t>275650</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MATER ADMIRABILIS</t>
+          <t>119 FELIPE ALVA Y ALVA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-6.750883</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-79.840113</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>-6.75915</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-79.85954</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>276032</t>
+          <t>275631</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ROSA FLORES DE OLIVA</t>
+          <t>002 MARAVILLAS DE JESUS</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-6.76938</t>
+          <t>479</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-79.86447</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>-6.7841</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-79.84052</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>275768</t>
+          <t>275626</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>10042 MONSEÑOR JUAN TOMIS STACK</t>
+          <t>049 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-6.76565</t>
+          <t>512</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-79.856812</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>-6.78322</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>-79.83533</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>276188</t>
+          <t>275612</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MANUEL PARDO</t>
+          <t>048 SEMILLLITAS DE JESUS</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-6.765613</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-79.842326</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>-6.76523</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-79.84604</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>275990</t>
+          <t>275551</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>031 ANGELITOS DEL CIELO</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-6.76624</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-79.82217</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-6.7705</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-79.871</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>275829</t>
+          <t>275527</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>11014 INMACULADA CONCEPCION</t>
+          <t>022 COSOMITO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-6.78359</t>
+          <t>431</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-79.83574</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>-6.76708</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-79.84975</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>276225</t>
+          <t>275495</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SANTA MARIA REINA</t>
+          <t>10021 SAN JOSE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-6.78525</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-79.84646</t>
+          <t>216</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>-6.774947</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-79.847868</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>275612</t>
+          <t>275457</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>048 SEMILLLITAS DE JESUS</t>
+          <t>004 ANGELITOS DE MARIA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-6.76523</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-79.84604</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-6.7787</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.8346</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>275650</t>
+          <t>275443</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>119 FELIPE ALVA Y ALVA</t>
+          <t>003 LOS PASTORCITOS DE LA VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-6.75915</t>
+          <t>386</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-79.85954</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-6.7642</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.8279</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>275669</t>
+          <t>275438</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>121 NUESTRA SEÑORA DEL PILAR</t>
+          <t>11004 SAN PEDRO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-6.77958</t>
+          <t>469</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-79.86658</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-6.760561</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.855511</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>278521</t>
+          <t>057671</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>024 LA INMACULADA</t>
+          <t>TRILCE CHICLAYO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-6.75102</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-79.83652</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-6.78336</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.84588</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>276046</t>
+          <t>056266</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PEDRO ABEL LABARTHE DURAND</t>
+          <t>G.M.V. COLLEGE / LUCERITOS DEL SABER / PINCELADAS DE COLORES</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-6.77495</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-79.84011</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>-6.78453</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-79.86287</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
